--- a/REVIEWED_mayor_bronson_20210728_20221115_20260513_autoPush.xlsx
+++ b/REVIEWED_mayor_bronson_20210728_20221115_20260513_autoPush.xlsx
@@ -31180,7 +31180,7 @@
         <v>0</v>
       </c>
       <c r="M602" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N602" t="inlineStr"/>
     </row>
